--- a/school_lublino/ceilling/vor_lublino_ceiling.xlsx
+++ b/school_lublino/ceilling/vor_lublino_ceiling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="5532" windowHeight="3396" tabRatio="790" firstSheet="6" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="5532" windowHeight="3396" tabRatio="790" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" state="hidden" r:id="rId1"/>
@@ -18,21 +18,23 @@
     <sheet name="1этВор" sheetId="10" state="hidden" r:id="rId4"/>
     <sheet name="1эт спец" sheetId="11" state="hidden" r:id="rId5"/>
     <sheet name="Вор2Вып" sheetId="12" state="hidden" r:id="rId6"/>
-    <sheet name="6.3П8" sheetId="20" r:id="rId7"/>
-    <sheet name="6.2П7,10" sheetId="19" r:id="rId8"/>
-    <sheet name="6.1П9" sheetId="18" r:id="rId9"/>
-    <sheet name="Общий" sheetId="13" r:id="rId10"/>
-    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId11"/>
-    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId12"/>
-    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId13"/>
-    <sheet name="ПокрПом" sheetId="16" r:id="rId14"/>
+    <sheet name="6.5П7,10 (2)" sheetId="22" r:id="rId7"/>
+    <sheet name="6.4П8" sheetId="21" r:id="rId8"/>
+    <sheet name="6.3П8" sheetId="20" r:id="rId9"/>
+    <sheet name="6.2П7,10" sheetId="19" r:id="rId10"/>
+    <sheet name="6.1П9" sheetId="18" r:id="rId11"/>
+    <sheet name="Общий" sheetId="13" r:id="rId12"/>
+    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId13"/>
+    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId15"/>
+    <sheet name="ПокрПом" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="186">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -579,6 +581,21 @@
   </si>
   <si>
     <t>3.013</t>
+  </si>
+  <si>
+    <t>1.049</t>
+  </si>
+  <si>
+    <t>1.050</t>
+  </si>
+  <si>
+    <t>1.051</t>
+  </si>
+  <si>
+    <t>2.085</t>
+  </si>
+  <si>
+    <t>Тип П-7</t>
   </si>
 </sst>
 </file>
@@ -589,7 +606,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -711,6 +728,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1289,7 +1315,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1791,6 +1817,18 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1812,15 +1850,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1874,6 +1912,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1951,7 +1992,7 @@
   <autoFilter ref="A2:E28">
     <filterColumn colId="3">
       <filters>
-        <filter val="12"/>
+        <filter val="10"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1974,7 +2015,7 @@
   <autoFilter ref="A32:E76">
     <filterColumn colId="3">
       <filters>
-        <filter val="15"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2526,6 +2567,715 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="199" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+    </row>
+    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="199" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="199"/>
+      <c r="I2" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="201"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="172">
+        <v>1</v>
+      </c>
+      <c r="B3" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="202" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="202"/>
+      <c r="K3" s="184">
+        <f>C9</f>
+        <v>292.98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="195" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="203"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="179" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="180">
+        <v>219.5</v>
+      </c>
+      <c r="D6" s="203"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="196"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="196"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="182" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="183">
+        <v>59.48</v>
+      </c>
+      <c r="D7" s="203"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="196"/>
+      <c r="H7" s="196"/>
+      <c r="I7" s="196"/>
+      <c r="J7" s="196"/>
+      <c r="K7" s="196"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="179" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="180">
+        <v>14</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="196"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="196"/>
+      <c r="H8" s="196"/>
+      <c r="I8" s="196"/>
+      <c r="J8" s="196"/>
+      <c r="K8" s="196"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="183">
+        <f>SUM(C6:C8)</f>
+        <v>292.98</v>
+      </c>
+      <c r="D9" s="203"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="196"/>
+      <c r="K9" s="196"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="D5:K9"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="199" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+    </row>
+    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="199" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="199"/>
+      <c r="I2" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="201"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="172">
+        <v>1</v>
+      </c>
+      <c r="B3" s="200" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="202" t="s">
+        <v>150</v>
+      </c>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="202"/>
+      <c r="K3" s="184">
+        <f>C10+G21+K10</f>
+        <v>258.09999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="195" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="196"/>
+      <c r="E5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="203"/>
+      <c r="I5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="K5" s="177" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="179" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="180">
+        <v>17.2</v>
+      </c>
+      <c r="D6" s="196"/>
+      <c r="E6" s="178">
+        <v>1</v>
+      </c>
+      <c r="F6" s="180" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="180">
+        <v>17.2</v>
+      </c>
+      <c r="H6" s="203"/>
+      <c r="I6" s="178">
+        <v>1</v>
+      </c>
+      <c r="J6" s="180" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="180">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="182" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="183">
+        <v>20.7</v>
+      </c>
+      <c r="D7" s="196"/>
+      <c r="E7" s="181">
+        <v>2</v>
+      </c>
+      <c r="F7" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="183">
+        <v>20.7</v>
+      </c>
+      <c r="H7" s="203"/>
+      <c r="I7" s="181">
+        <v>2</v>
+      </c>
+      <c r="J7" s="183" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="183">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="179" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="180">
+        <v>5.5</v>
+      </c>
+      <c r="D8" s="196"/>
+      <c r="E8" s="178">
+        <v>3</v>
+      </c>
+      <c r="F8" s="180" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="180">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="203"/>
+      <c r="I8" s="178">
+        <v>3</v>
+      </c>
+      <c r="J8" s="180" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="180">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="182" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="183">
+        <v>3</v>
+      </c>
+      <c r="D9" s="196"/>
+      <c r="E9" s="181">
+        <v>4</v>
+      </c>
+      <c r="F9" s="183" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="183">
+        <v>3</v>
+      </c>
+      <c r="H9" s="203"/>
+      <c r="I9" s="181">
+        <v>4</v>
+      </c>
+      <c r="J9" s="183" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="183">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="178"/>
+      <c r="B10" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="183">
+        <f>SUM(C6:C9)</f>
+        <v>46.4</v>
+      </c>
+      <c r="D10" s="196"/>
+      <c r="E10" s="178">
+        <v>5</v>
+      </c>
+      <c r="F10" s="180" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="180">
+        <v>6.08</v>
+      </c>
+      <c r="H10" s="203"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="K10" s="183">
+        <f>SUM(K6:K9)</f>
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="198"/>
+      <c r="B11" s="198"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="196"/>
+      <c r="E11" s="181">
+        <v>6</v>
+      </c>
+      <c r="F11" s="183" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="183">
+        <v>12.15</v>
+      </c>
+      <c r="H11" s="203"/>
+      <c r="I11" s="198"/>
+      <c r="J11" s="198"/>
+      <c r="K11" s="198"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="197"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="178">
+        <v>7</v>
+      </c>
+      <c r="F12" s="180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="180">
+        <v>10.67</v>
+      </c>
+      <c r="H12" s="203"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="197"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="197"/>
+      <c r="B13" s="197"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="196"/>
+      <c r="E13" s="181">
+        <v>8</v>
+      </c>
+      <c r="F13" s="183" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="183">
+        <v>8.81</v>
+      </c>
+      <c r="H13" s="203"/>
+      <c r="I13" s="197"/>
+      <c r="J13" s="197"/>
+      <c r="K13" s="197"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="197"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="178">
+        <v>9</v>
+      </c>
+      <c r="F14" s="179" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="180">
+        <v>14.23</v>
+      </c>
+      <c r="H14" s="203"/>
+      <c r="I14" s="197"/>
+      <c r="J14" s="197"/>
+      <c r="K14" s="197"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="197"/>
+      <c r="B15" s="197"/>
+      <c r="C15" s="197"/>
+      <c r="D15" s="196"/>
+      <c r="E15" s="181">
+        <v>10</v>
+      </c>
+      <c r="F15" s="183" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="183">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="H15" s="203"/>
+      <c r="I15" s="197"/>
+      <c r="J15" s="197"/>
+      <c r="K15" s="197"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="197"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="196"/>
+      <c r="E16" s="178">
+        <v>11</v>
+      </c>
+      <c r="F16" s="180" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="180">
+        <v>12.22</v>
+      </c>
+      <c r="H16" s="203"/>
+      <c r="I16" s="197"/>
+      <c r="J16" s="197"/>
+      <c r="K16" s="197"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="197"/>
+      <c r="B17" s="197"/>
+      <c r="C17" s="197"/>
+      <c r="D17" s="196"/>
+      <c r="E17" s="181">
+        <v>12</v>
+      </c>
+      <c r="F17" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="183">
+        <v>8.35</v>
+      </c>
+      <c r="H17" s="203"/>
+      <c r="I17" s="197"/>
+      <c r="J17" s="197"/>
+      <c r="K17" s="197"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="197"/>
+      <c r="B18" s="197"/>
+      <c r="C18" s="197"/>
+      <c r="D18" s="196"/>
+      <c r="E18" s="178">
+        <v>13</v>
+      </c>
+      <c r="F18" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="180">
+        <v>14.03</v>
+      </c>
+      <c r="H18" s="203"/>
+      <c r="I18" s="197"/>
+      <c r="J18" s="197"/>
+      <c r="K18" s="197"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="197"/>
+      <c r="B19" s="197"/>
+      <c r="C19" s="197"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="181">
+        <v>12</v>
+      </c>
+      <c r="F19" s="183" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="183">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H19" s="203"/>
+      <c r="I19" s="197"/>
+      <c r="J19" s="197"/>
+      <c r="K19" s="197"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="197"/>
+      <c r="B20" s="197"/>
+      <c r="C20" s="197"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="178">
+        <v>13</v>
+      </c>
+      <c r="F20" s="179" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="180">
+        <v>16.2</v>
+      </c>
+      <c r="H20" s="203"/>
+      <c r="I20" s="197"/>
+      <c r="J20" s="197"/>
+      <c r="K20" s="197"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="197"/>
+      <c r="B21" s="197"/>
+      <c r="C21" s="197"/>
+      <c r="D21" s="196"/>
+      <c r="F21" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="183">
+        <f>SUM(G6:G20)</f>
+        <v>165.29999999999998</v>
+      </c>
+      <c r="H21" s="203"/>
+      <c r="I21" s="197"/>
+      <c r="J21" s="197"/>
+      <c r="K21" s="197"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A11:C21"/>
+    <mergeCell ref="I11:K21"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="D5:D21"/>
+    <mergeCell ref="H5:H21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -2540,19 +3290,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="202"/>
-      <c r="G1" s="203" t="s">
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="206"/>
+      <c r="G1" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="205"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="209"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="117" t="s">
@@ -2727,9 +3477,9 @@
       <c r="J7">
         <v>38.21</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="e">
         <f>--MID($L$6,IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2),FIND("; ",$L$6&amp;"; ",IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2))-IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2))</f>
-        <v>3.0150000000000001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2760,9 +3510,9 @@
       <c r="J8">
         <v>596.26</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="e">
         <f t="shared" ref="L8:L19" si="0">--MID($L$6,IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2),FIND("; ",$L$6&amp;"; ",IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2))-IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2))</f>
-        <v>3.016</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2793,9 +3543,9 @@
       <c r="J9">
         <v>156.6</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="e">
         <f t="shared" si="0"/>
-        <v>3.0169999999999999</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2826,9 +3576,9 @@
       <c r="J10">
         <v>46.57</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="e">
         <f t="shared" si="0"/>
-        <v>3.0179999999999998</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3141,7 +3891,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3158,7 +3908,7 @@
         <v>220.47</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3175,7 +3925,7 @@
         <v>61.99</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3196,7 +3946,7 @@
         <v>14.29999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3215,19 +3965,19 @@
       <c r="F28" s="121"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="200" t="s">
+      <c r="A31" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="201"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="202"/>
-      <c r="G31" s="203" t="s">
+      <c r="B31" s="205"/>
+      <c r="C31" s="205"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="206"/>
+      <c r="G31" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H31" s="204"/>
-      <c r="I31" s="204"/>
-      <c r="J31" s="205"/>
+      <c r="H31" s="208"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="209"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="117" t="s">
@@ -3371,7 +4121,7 @@
         <v>306.63</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>43</v>
       </c>
@@ -3783,7 +4533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>19</v>
       </c>
@@ -4103,7 +4853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>44</v>
       </c>
@@ -4121,19 +4871,19 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="200" t="s">
+      <c r="A80" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="201"/>
-      <c r="C80" s="201"/>
-      <c r="D80" s="201"/>
-      <c r="E80" s="202"/>
-      <c r="G80" s="203" t="s">
+      <c r="B80" s="205"/>
+      <c r="C80" s="205"/>
+      <c r="D80" s="205"/>
+      <c r="E80" s="206"/>
+      <c r="G80" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="204"/>
-      <c r="I80" s="204"/>
-      <c r="J80" s="205"/>
+      <c r="H80" s="208"/>
+      <c r="I80" s="208"/>
+      <c r="J80" s="209"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="117" t="s">
@@ -4705,7 +5455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4805,7 +5555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4817,13 +5567,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="205"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="209"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="122" t="s">
@@ -4965,7 +5715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -5372,7 +6122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -5381,13 +6131,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
@@ -5487,13 +6237,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
+      <c r="B8" s="210"/>
+      <c r="C8" s="210"/>
+      <c r="D8" s="210"/>
+      <c r="E8" s="210"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="142" t="s">
@@ -5695,13 +6445,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="206" t="s">
+      <c r="A21" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="206"/>
-      <c r="C21" s="206"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="206"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="210"/>
+      <c r="D21" s="210"/>
+      <c r="E21" s="210"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="142" t="s">
@@ -5813,13 +6563,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="212" t="s">
+      <c r="A30" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="212"/>
-      <c r="C30" s="212"/>
-      <c r="D30" s="212"/>
-      <c r="E30" s="212"/>
+      <c r="B30" s="216"/>
+      <c r="C30" s="216"/>
+      <c r="D30" s="216"/>
+      <c r="E30" s="216"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="150" t="s">
@@ -5856,13 +6606,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="209" t="s">
+      <c r="A33" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="210"/>
-      <c r="C33" s="210"/>
-      <c r="D33" s="210"/>
-      <c r="E33" s="211"/>
+      <c r="B33" s="214"/>
+      <c r="C33" s="214"/>
+      <c r="D33" s="214"/>
+      <c r="E33" s="215"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="150" t="s">
@@ -5957,13 +6707,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="207" t="s">
+      <c r="A42" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="207"/>
-      <c r="C42" s="207"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="207"/>
+      <c r="B42" s="211"/>
+      <c r="C42" s="211"/>
+      <c r="D42" s="211"/>
+      <c r="E42" s="211"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="162" t="s">
@@ -6097,13 +6847,13 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="207" t="s">
+      <c r="A51" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="207"/>
-      <c r="C51" s="207"/>
-      <c r="D51" s="207"/>
-      <c r="E51" s="207"/>
+      <c r="B51" s="211"/>
+      <c r="C51" s="211"/>
+      <c r="D51" s="211"/>
+      <c r="E51" s="211"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="162" t="s">
@@ -6220,13 +6970,13 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="207" t="s">
+      <c r="A59" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="207"/>
-      <c r="C59" s="207"/>
-      <c r="D59" s="207"/>
-      <c r="E59" s="207"/>
+      <c r="B59" s="211"/>
+      <c r="C59" s="211"/>
+      <c r="D59" s="211"/>
+      <c r="E59" s="211"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="162" t="s">
@@ -6338,13 +7088,13 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="185" t="s">
+      <c r="A68" s="189" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="185"/>
-      <c r="C68" s="185"/>
-      <c r="D68" s="185"/>
-      <c r="E68" s="185"/>
+      <c r="B68" s="189"/>
+      <c r="C68" s="189"/>
+      <c r="D68" s="189"/>
+      <c r="E68" s="189"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="123" t="s">
@@ -6381,13 +7131,13 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="208" t="s">
+      <c r="A73" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="208"/>
-      <c r="C73" s="208"/>
-      <c r="D73" s="208"/>
-      <c r="E73" s="208"/>
+      <c r="B73" s="212"/>
+      <c r="C73" s="212"/>
+      <c r="D73" s="212"/>
+      <c r="E73" s="212"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="156" t="s">
@@ -6470,13 +7220,13 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="208" t="s">
+      <c r="A79" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="208"/>
-      <c r="C79" s="208"/>
-      <c r="D79" s="208"/>
-      <c r="E79" s="208"/>
+      <c r="B79" s="212"/>
+      <c r="C79" s="212"/>
+      <c r="D79" s="212"/>
+      <c r="E79" s="212"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="156" t="s">
@@ -6525,13 +7275,13 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="206" t="s">
+      <c r="A85" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="206"/>
-      <c r="C85" s="206"/>
-      <c r="D85" s="206"/>
-      <c r="E85" s="206"/>
+      <c r="B85" s="210"/>
+      <c r="C85" s="210"/>
+      <c r="D85" s="210"/>
+      <c r="E85" s="210"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="142" t="s">
@@ -6568,13 +7318,13 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="206" t="s">
+      <c r="A88" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="206"/>
-      <c r="C88" s="206"/>
-      <c r="D88" s="206"/>
-      <c r="E88" s="206"/>
+      <c r="B88" s="210"/>
+      <c r="C88" s="210"/>
+      <c r="D88" s="210"/>
+      <c r="E88" s="210"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="142" t="s">
@@ -6640,13 +7390,13 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="206" t="s">
+      <c r="A93" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="206"/>
-      <c r="C93" s="206"/>
-      <c r="D93" s="206"/>
-      <c r="E93" s="206"/>
+      <c r="B93" s="210"/>
+      <c r="C93" s="210"/>
+      <c r="D93" s="210"/>
+      <c r="E93" s="210"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="142" t="s">
@@ -6759,25 +7509,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="189" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="190" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="188"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="192"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -7554,18 +8304,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
+      <c r="B2" s="194"/>
+      <c r="C2" s="194"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -8727,6 +9477,375 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" customWidth="1"/>
+    <col min="10" max="10" width="2.88671875" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="199" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+    </row>
+    <row r="2" spans="1:11" s="188" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="199" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="199"/>
+      <c r="I2" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="201"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="187">
+        <v>1</v>
+      </c>
+      <c r="B3" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="202" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="202"/>
+      <c r="K3" s="184">
+        <f>C7</f>
+        <v>167.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="195"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="203"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="179" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="180">
+        <v>167.53</v>
+      </c>
+      <c r="D6" s="203"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="196"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="196"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="182" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="183">
+        <f>SUM(C6:C6)</f>
+        <v>167.53</v>
+      </c>
+      <c r="D7" s="203"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="196"/>
+      <c r="H7" s="196"/>
+      <c r="I7" s="196"/>
+      <c r="J7" s="196"/>
+      <c r="K7" s="196"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="199" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+    </row>
+    <row r="2" spans="1:11" s="185" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="199" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="199"/>
+      <c r="I2" s="201" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="201"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="186">
+        <v>1</v>
+      </c>
+      <c r="B3" s="200" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="202" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="202"/>
+      <c r="K3" s="184">
+        <f>C9</f>
+        <v>155.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="217"/>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="217"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="217"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="203"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="180">
+        <v>102.83</v>
+      </c>
+      <c r="D6" s="203"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="196"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="196"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="183">
+        <v>21.8</v>
+      </c>
+      <c r="D7" s="203"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="196"/>
+      <c r="H7" s="196"/>
+      <c r="I7" s="196"/>
+      <c r="J7" s="196"/>
+      <c r="K7" s="196"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="178" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="180">
+        <v>30.72</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="196"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="196"/>
+      <c r="H8" s="196"/>
+      <c r="I8" s="196"/>
+      <c r="J8" s="196"/>
+      <c r="K8" s="196"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="182"/>
+      <c r="B9" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="183">
+        <f>SUM(C6:C8)</f>
+        <v>155.35</v>
+      </c>
+      <c r="D9" s="203"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="196"/>
+      <c r="K9" s="196"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:K9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8742,39 +9861,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="196" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="195" t="s">
+      <c r="B2" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="199" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="195"/>
-      <c r="I2" s="197" t="s">
+      <c r="H2" s="199"/>
+      <c r="I2" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="197"/>
+      <c r="J2" s="201"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -8783,40 +9902,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="200" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="198" t="s">
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="202" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198" t="s">
+      <c r="H3" s="202"/>
+      <c r="I3" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="198"/>
+      <c r="J3" s="202"/>
       <c r="K3" s="184">
         <f>C13+G15+K16</f>
         <v>1966.37</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="195" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -8828,7 +9947,7 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="194"/>
+      <c r="D5" s="196"/>
       <c r="E5" s="175" t="s">
         <v>0</v>
       </c>
@@ -8838,7 +9957,7 @@
       <c r="G5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="193"/>
+      <c r="H5" s="197"/>
       <c r="I5" s="175" t="s">
         <v>0</v>
       </c>
@@ -8859,7 +9978,7 @@
       <c r="C6" s="180">
         <v>114.21</v>
       </c>
-      <c r="D6" s="194"/>
+      <c r="D6" s="196"/>
       <c r="E6" s="178">
         <v>1</v>
       </c>
@@ -8869,7 +9988,7 @@
       <c r="G6" s="180">
         <v>73.599999999999994</v>
       </c>
-      <c r="H6" s="193"/>
+      <c r="H6" s="197"/>
       <c r="I6" s="178">
         <v>1</v>
       </c>
@@ -8890,7 +10009,7 @@
       <c r="C7" s="183">
         <v>68.75</v>
       </c>
-      <c r="D7" s="194"/>
+      <c r="D7" s="196"/>
       <c r="E7" s="181">
         <v>2</v>
       </c>
@@ -8900,7 +10019,7 @@
       <c r="G7" s="183">
         <v>72.16</v>
       </c>
-      <c r="H7" s="193"/>
+      <c r="H7" s="197"/>
       <c r="I7" s="181">
         <v>2</v>
       </c>
@@ -8921,7 +10040,7 @@
       <c r="C8" s="180">
         <v>68.81</v>
       </c>
-      <c r="D8" s="194"/>
+      <c r="D8" s="196"/>
       <c r="E8" s="178">
         <v>3</v>
       </c>
@@ -8931,7 +10050,7 @@
       <c r="G8" s="180">
         <v>68.27</v>
       </c>
-      <c r="H8" s="193"/>
+      <c r="H8" s="197"/>
       <c r="I8" s="178">
         <v>3</v>
       </c>
@@ -8952,7 +10071,7 @@
       <c r="C9" s="183">
         <v>69.069999999999993</v>
       </c>
-      <c r="D9" s="194"/>
+      <c r="D9" s="196"/>
       <c r="E9" s="181">
         <v>4</v>
       </c>
@@ -8962,7 +10081,7 @@
       <c r="G9" s="183">
         <v>68.3</v>
       </c>
-      <c r="H9" s="193"/>
+      <c r="H9" s="197"/>
       <c r="I9" s="181">
         <v>4</v>
       </c>
@@ -8983,7 +10102,7 @@
       <c r="C10" s="180">
         <v>68.78</v>
       </c>
-      <c r="D10" s="194"/>
+      <c r="D10" s="196"/>
       <c r="E10" s="178">
         <v>5</v>
       </c>
@@ -8993,7 +10112,7 @@
       <c r="G10" s="180">
         <v>68.64</v>
       </c>
-      <c r="H10" s="193"/>
+      <c r="H10" s="197"/>
       <c r="I10" s="178">
         <v>5</v>
       </c>
@@ -9014,7 +10133,7 @@
       <c r="C11" s="183">
         <v>68.03</v>
       </c>
-      <c r="D11" s="194"/>
+      <c r="D11" s="196"/>
       <c r="E11" s="181">
         <v>6</v>
       </c>
@@ -9024,7 +10143,7 @@
       <c r="G11" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H11" s="193"/>
+      <c r="H11" s="197"/>
       <c r="I11" s="181">
         <v>6</v>
       </c>
@@ -9045,7 +10164,7 @@
       <c r="C12" s="180">
         <v>137.58000000000001</v>
       </c>
-      <c r="D12" s="194"/>
+      <c r="D12" s="196"/>
       <c r="E12" s="178">
         <v>7</v>
       </c>
@@ -9055,7 +10174,7 @@
       <c r="G12" s="180">
         <v>67.58</v>
       </c>
-      <c r="H12" s="193"/>
+      <c r="H12" s="197"/>
       <c r="I12" s="178">
         <v>7</v>
       </c>
@@ -9075,7 +10194,7 @@
         <f>SUM(C6:C12)</f>
         <v>595.23</v>
       </c>
-      <c r="D13" s="194"/>
+      <c r="D13" s="196"/>
       <c r="E13" s="181">
         <v>8</v>
       </c>
@@ -9085,7 +10204,7 @@
       <c r="G13" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H13" s="193"/>
+      <c r="H13" s="197"/>
       <c r="I13" s="181">
         <v>8</v>
       </c>
@@ -9097,10 +10216,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="194"/>
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="196"/>
       <c r="E14" s="178">
         <v>9</v>
       </c>
@@ -9110,7 +10229,7 @@
       <c r="G14" s="180">
         <v>68.27</v>
       </c>
-      <c r="H14" s="193"/>
+      <c r="H14" s="197"/>
       <c r="I14" s="178">
         <v>9</v>
       </c>
@@ -9122,10 +10241,10 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="194"/>
+      <c r="A15" s="197"/>
+      <c r="B15" s="197"/>
+      <c r="C15" s="197"/>
+      <c r="D15" s="196"/>
       <c r="F15" s="182" t="s">
         <v>93</v>
       </c>
@@ -9133,7 +10252,7 @@
         <f>SUM(G6:G14)</f>
         <v>623.7399999999999</v>
       </c>
-      <c r="H15" s="193"/>
+      <c r="H15" s="197"/>
       <c r="I15" s="181">
         <v>10</v>
       </c>
@@ -9145,14 +10264,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="193"/>
-      <c r="F16" s="193"/>
-      <c r="G16" s="193"/>
-      <c r="H16" s="193"/>
+      <c r="A16" s="197"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="196"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="197"/>
+      <c r="G16" s="197"/>
+      <c r="H16" s="197"/>
       <c r="J16" s="182" t="s">
         <v>93</v>
       </c>
@@ -9179,713 +10298,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" customWidth="1"/>
-    <col min="9" max="10" width="8.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="195" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-    </row>
-    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="196" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="195" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="195"/>
-      <c r="I2" s="197" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="197"/>
-      <c r="K2" s="173" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="172">
-        <v>1</v>
-      </c>
-      <c r="B3" s="196" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="198" t="s">
-        <v>161</v>
-      </c>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="198"/>
-      <c r="K3" s="184">
-        <f>C9</f>
-        <v>292.98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="191" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="199"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
-      <c r="K5" s="194"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="179" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="180">
-        <v>219.5</v>
-      </c>
-      <c r="D6" s="199"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="194"/>
-      <c r="K6" s="194"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
-        <v>2</v>
-      </c>
-      <c r="B7" s="182" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="183">
-        <v>59.48</v>
-      </c>
-      <c r="D7" s="199"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="178">
-        <v>3</v>
-      </c>
-      <c r="B8" s="179" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="180">
-        <v>14</v>
-      </c>
-      <c r="D8" s="199"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="194"/>
-      <c r="K8" s="194"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="182" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="183">
-        <f>SUM(C6:C8)</f>
-        <v>292.98</v>
-      </c>
-      <c r="D9" s="199"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="194"/>
-      <c r="K9" s="194"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="D5:K9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" customWidth="1"/>
-    <col min="9" max="10" width="8.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="195" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-    </row>
-    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="196" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="195" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="195"/>
-      <c r="I2" s="197" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="197"/>
-      <c r="K2" s="173" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="172">
-        <v>1</v>
-      </c>
-      <c r="B3" s="196" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="198" t="s">
-        <v>150</v>
-      </c>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="198"/>
-      <c r="K3" s="184">
-        <f>C10+G21+K10</f>
-        <v>258.09999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="191" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="194"/>
-      <c r="E5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="199"/>
-      <c r="I5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="177" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="179" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="180">
-        <v>17.2</v>
-      </c>
-      <c r="D6" s="194"/>
-      <c r="E6" s="178">
-        <v>1</v>
-      </c>
-      <c r="F6" s="180" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="180">
-        <v>17.2</v>
-      </c>
-      <c r="H6" s="199"/>
-      <c r="I6" s="178">
-        <v>1</v>
-      </c>
-      <c r="J6" s="180" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="180">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
-        <v>2</v>
-      </c>
-      <c r="B7" s="182" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="183">
-        <v>20.7</v>
-      </c>
-      <c r="D7" s="194"/>
-      <c r="E7" s="181">
-        <v>2</v>
-      </c>
-      <c r="F7" s="183" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="183">
-        <v>20.7</v>
-      </c>
-      <c r="H7" s="199"/>
-      <c r="I7" s="181">
-        <v>2</v>
-      </c>
-      <c r="J7" s="183" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="183">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="178">
-        <v>3</v>
-      </c>
-      <c r="B8" s="179" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="180">
-        <v>5.5</v>
-      </c>
-      <c r="D8" s="194"/>
-      <c r="E8" s="178">
-        <v>3</v>
-      </c>
-      <c r="F8" s="180" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="180">
-        <v>5.5</v>
-      </c>
-      <c r="H8" s="199"/>
-      <c r="I8" s="178">
-        <v>3</v>
-      </c>
-      <c r="J8" s="180" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="180">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="181">
-        <v>4</v>
-      </c>
-      <c r="B9" s="182" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="183">
-        <v>3</v>
-      </c>
-      <c r="D9" s="194"/>
-      <c r="E9" s="181">
-        <v>4</v>
-      </c>
-      <c r="F9" s="183" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="183">
-        <v>3</v>
-      </c>
-      <c r="H9" s="199"/>
-      <c r="I9" s="181">
-        <v>4</v>
-      </c>
-      <c r="J9" s="183" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="183">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="178"/>
-      <c r="B10" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="183">
-        <f>SUM(C6:C9)</f>
-        <v>46.4</v>
-      </c>
-      <c r="D10" s="194"/>
-      <c r="E10" s="178">
-        <v>5</v>
-      </c>
-      <c r="F10" s="180" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="180">
-        <v>6.08</v>
-      </c>
-      <c r="H10" s="199"/>
-      <c r="I10" s="178"/>
-      <c r="J10" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" s="183">
-        <f>SUM(K6:K9)</f>
-        <v>46.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="192"/>
-      <c r="B11" s="192"/>
-      <c r="C11" s="192"/>
-      <c r="D11" s="194"/>
-      <c r="E11" s="181">
-        <v>6</v>
-      </c>
-      <c r="F11" s="183" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="183">
-        <v>12.15</v>
-      </c>
-      <c r="H11" s="199"/>
-      <c r="I11" s="192"/>
-      <c r="J11" s="192"/>
-      <c r="K11" s="192"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="193"/>
-      <c r="B12" s="193"/>
-      <c r="C12" s="193"/>
-      <c r="D12" s="194"/>
-      <c r="E12" s="178">
-        <v>7</v>
-      </c>
-      <c r="F12" s="180" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="180">
-        <v>10.67</v>
-      </c>
-      <c r="H12" s="199"/>
-      <c r="I12" s="193"/>
-      <c r="J12" s="193"/>
-      <c r="K12" s="193"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="193"/>
-      <c r="B13" s="193"/>
-      <c r="C13" s="193"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="181">
-        <v>8</v>
-      </c>
-      <c r="F13" s="183" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="183">
-        <v>8.81</v>
-      </c>
-      <c r="H13" s="199"/>
-      <c r="I13" s="193"/>
-      <c r="J13" s="193"/>
-      <c r="K13" s="193"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="178">
-        <v>9</v>
-      </c>
-      <c r="F14" s="179" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="180">
-        <v>14.23</v>
-      </c>
-      <c r="H14" s="199"/>
-      <c r="I14" s="193"/>
-      <c r="J14" s="193"/>
-      <c r="K14" s="193"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="181">
-        <v>10</v>
-      </c>
-      <c r="F15" s="183" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="183">
-        <v>8.1300000000000008</v>
-      </c>
-      <c r="H15" s="199"/>
-      <c r="I15" s="193"/>
-      <c r="J15" s="193"/>
-      <c r="K15" s="193"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="178">
-        <v>11</v>
-      </c>
-      <c r="F16" s="180" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="180">
-        <v>12.22</v>
-      </c>
-      <c r="H16" s="199"/>
-      <c r="I16" s="193"/>
-      <c r="J16" s="193"/>
-      <c r="K16" s="193"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="193"/>
-      <c r="B17" s="193"/>
-      <c r="C17" s="193"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="181">
-        <v>12</v>
-      </c>
-      <c r="F17" s="183" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="183">
-        <v>8.35</v>
-      </c>
-      <c r="H17" s="199"/>
-      <c r="I17" s="193"/>
-      <c r="J17" s="193"/>
-      <c r="K17" s="193"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="193"/>
-      <c r="B18" s="193"/>
-      <c r="C18" s="193"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="178">
-        <v>13</v>
-      </c>
-      <c r="F18" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="180">
-        <v>14.03</v>
-      </c>
-      <c r="H18" s="199"/>
-      <c r="I18" s="193"/>
-      <c r="J18" s="193"/>
-      <c r="K18" s="193"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="193"/>
-      <c r="B19" s="193"/>
-      <c r="C19" s="193"/>
-      <c r="D19" s="194"/>
-      <c r="E19" s="181">
-        <v>12</v>
-      </c>
-      <c r="F19" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="183">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="H19" s="199"/>
-      <c r="I19" s="193"/>
-      <c r="J19" s="193"/>
-      <c r="K19" s="193"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="193"/>
-      <c r="B20" s="193"/>
-      <c r="C20" s="193"/>
-      <c r="D20" s="194"/>
-      <c r="E20" s="178">
-        <v>13</v>
-      </c>
-      <c r="F20" s="179" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="180">
-        <v>16.2</v>
-      </c>
-      <c r="H20" s="199"/>
-      <c r="I20" s="193"/>
-      <c r="J20" s="193"/>
-      <c r="K20" s="193"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="193"/>
-      <c r="B21" s="193"/>
-      <c r="C21" s="193"/>
-      <c r="D21" s="194"/>
-      <c r="F21" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="183">
-        <f>SUM(G6:G20)</f>
-        <v>165.29999999999998</v>
-      </c>
-      <c r="H21" s="199"/>
-      <c r="I21" s="193"/>
-      <c r="J21" s="193"/>
-      <c r="K21" s="193"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A11:C21"/>
-    <mergeCell ref="I11:K21"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="D5:D21"/>
-    <mergeCell ref="H5:H21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>